--- a/Design/Excel/ET/Datas/Product/StationConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/StationConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1183,6 +1183,16 @@
           <t>Capabilities</t>
         </is>
       </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>WaterDefinitionId</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>WaterUnits</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1225,6 +1235,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1267,6 +1287,16 @@
           <t>Capabilities</t>
         </is>
       </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>WaterDefinitionId</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>WaterUnits</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1309,6 +1339,12 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I4" s="0">
+        <v>0</v>
+      </c>
+      <c r="J4" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1351,6 +1387,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="I5" s="0">
+        <v>0</v>
+      </c>
+      <c r="J5" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1393,6 +1435,12 @@
           <t>2</t>
         </is>
       </c>
+      <c r="I6" s="0">
+        <v>0</v>
+      </c>
+      <c r="J6" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1435,6 +1483,12 @@
           <t>4</t>
         </is>
       </c>
+      <c r="I7" s="0">
+        <v>0</v>
+      </c>
+      <c r="J7" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1477,6 +1531,12 @@
           <t>8</t>
         </is>
       </c>
+      <c r="I8" s="0">
+        <v>0</v>
+      </c>
+      <c r="J8" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1491,7 +1551,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>洗碗台</t>
+          <t>水池／洗碗台</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1514,10 +1574,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="H9">
+        <v>400</v>
+      </c>
+      <c r="I9" s="0">
+        <v>11</v>
+      </c>
+      <c r="J9" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1561,6 +1625,12 @@
           <t>32</t>
         </is>
       </c>
+      <c r="I10" s="0">
+        <v>0</v>
+      </c>
+      <c r="J10" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1602,6 +1672,52 @@
         <is>
           <t>64</t>
         </is>
+      </c>
+      <c r="I11" s="0">
+        <v>0</v>
+      </c>
+      <c r="J11" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>垃圾桶</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0,1,1,0,0,-1,-1,0</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>512</v>
+      </c>
+      <c r="I12" s="0">
+        <v>0</v>
+      </c>
+      <c r="J12" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/Product/StationConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/StationConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1720,6 +1720,102 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>榨汁机</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0,1,1,0,0,-1,-1,0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="I13" s="0">
+        <v>0</v>
+      </c>
+      <c r="J13" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>贴单台</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0,1,1,0,0,-1,-1,0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="I14" s="0">
+        <v>0</v>
+      </c>
+      <c r="J14" s="0">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Design/Excel/ET/Datas/Product/StationConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/StationConfig.xlsx
@@ -939,845 +939,871 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <x:cols>
-    <x:col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <x:col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <x:col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <x:col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <x:col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <x:col min="7" max="7" width="28.75" style="2" customWidth="1"/>
-    <x:col min="8" max="9" width="11.75" style="2" customWidth="1"/>
-    <x:col min="10" max="10" width="6.75" style="2" customWidth="1"/>
-    <x:col min="11" max="16384" width="9" style="2" customWidth="0"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##var</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Kind</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FootprintOffsets</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ApproachOffsets</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ItemSlotCapacity</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Capabilities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">WaterDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">WaterUnits</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##type</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(list#sep=,),int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(list#sep=,),int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Kind</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FootprintOffsets</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ApproachOffsets</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ItemSlotCapacity</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Capabilities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">WaterDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">WaterUnits</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">台面</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,1,1,0,0,-1,-1,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I4">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J4">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">切配台</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,1,1,0,0,-1,-1,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J5">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">灶台</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,1,1,0,0,-1,-1,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I6">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J6">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">烤箱</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,0,0,1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-1,0,1,0,0,-1,-1,1,1,1,0,2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J7">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">餐桌</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,1,1,0,0,-1,-1,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">8</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J8">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">水池／洗碗台</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,1,1,0,0,-1,-1,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H9">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="I9">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="J9">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">脏餐具池</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,1,1,0,0,-1,-1,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">32</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I10">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J10">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">8</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">干净餐具池</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,1,1,0,0,-1,-1,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">64</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J11">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B12">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">垃圾桶</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D12">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,1,1,0,0,-1,-1,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G12">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12">
-        <x:v>512</x:v>
-      </x:c>
-      <x:c r="I12">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J12">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">榨汁机</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">9</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,1,1,0,0,-1,-1,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1024</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I13">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J13">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">11</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">贴单台</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0,1,1,0,0,-1,-1,0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2048</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I14">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J14">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str"/>
-      <x:c r="B15" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C15" t="str">
-        <x:v>煎台</x:v>
-      </x:c>
-      <x:c r="D15" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E15" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="F15" t="str">
-        <x:v>0,1,1,0,0,-1,-1,0</x:v>
-      </x:c>
-      <x:c r="G15" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" t="n">
-        <x:v>4096</x:v>
-      </x:c>
-      <x:c r="I15" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J15" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="str"/>
-      <x:c r="B16" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" t="str">
-        <x:v>搅拌机</x:v>
-      </x:c>
-      <x:c r="D16" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E16" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="F16" t="str">
-        <x:v>0,1,1,0,0,-1,-1,0</x:v>
-      </x:c>
-      <x:c r="G16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" t="n">
-        <x:v>8192</x:v>
-      </x:c>
-      <x:c r="I16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="str"/>
-      <x:c r="B17" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C17" t="str">
-        <x:v>磨豆机</x:v>
-      </x:c>
-      <x:c r="D17" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E17" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="F17" t="str">
-        <x:v>0,1,1,0,0,-1,-1,0</x:v>
-      </x:c>
-      <x:c r="G17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" t="n">
-        <x:v>16384</x:v>
-      </x:c>
-      <x:c r="I17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="str"/>
-      <x:c r="B18" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C18" t="str">
-        <x:v>咖啡机</x:v>
-      </x:c>
-      <x:c r="D18" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E18" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="F18" t="str">
-        <x:v>0,1,1,0,0,-1,-1,0</x:v>
-      </x:c>
-      <x:c r="G18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" t="n">
-        <x:v>32768</x:v>
-      </x:c>
-      <x:c r="I18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="str"/>
-      <x:c r="B19" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C19" t="str">
-        <x:v>蒸汽机</x:v>
-      </x:c>
-      <x:c r="D19" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E19" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="F19" t="str">
-        <x:v>0,1,1,0,0,-1,-1,0</x:v>
-      </x:c>
-      <x:c r="G19" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" t="n">
-        <x:v>196608</x:v>
-      </x:c>
-      <x:c r="I19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
+    <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
+    <col min="8" max="9" width="11.75" style="2" customWidth="1"/>
+    <col min="10" max="10" width="6.75" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2" customWidth="0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kind</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FootprintOffsets</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ApproachOffsets</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ItemSlotCapacity</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capabilities</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WaterDefinitionId</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WaterUnits</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>GridStationKind</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(list#sep=,),int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(list#sep=,),int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>GridStationCapability</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kind</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FootprintOffsets</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ApproachOffsets</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ItemSlotCapacity</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capabilities</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WaterDefinitionId</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WaterUnits</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台面</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Counter</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,1,1,0,0,-1,-1,0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">切配台</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Chopping</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,1,1,0,0,-1,-1,0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Chop</t>
+        </is>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">灶台</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stove</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,1,1,0,0,-1,-1,0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Cook</t>
+        </is>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">烤箱</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Oven</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,0,0,1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-1,0,1,0,0,-1,-1,1,1,1,0,2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bake</t>
+        </is>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">餐桌</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,1,1,0,0,-1,-1,0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Serve</t>
+        </is>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">水池／洗碗台</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Wash</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,1,1,0,0,-1,-1,0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Wash|FillWater|DrainLiquid</t>
+        </is>
+      </c>
+      <c r="I9">
+        <v>11</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">脏餐具池</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DirtyPool</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,1,1,0,0,-1,-1,0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>DirtyPool</t>
+        </is>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">干净餐具池</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CleanPool</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,1,1,0,0,-1,-1,0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CleanPool</t>
+        </is>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">垃圾桶</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Trash</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,1,1,0,0,-1,-1,0</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Trash</t>
+        </is>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">榨汁机</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,1,1,0,0,-1,-1,0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Juice</t>
+        </is>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">贴单台</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LabelDesk</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,1,1,0,0,-1,-1,0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>LabelDrink</t>
+        </is>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str"/>
+      <c r="B15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" t="str">
+        <v>煎台</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Frying</t>
+        </is>
+      </c>
+      <c r="E15" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="F15" t="str">
+        <v>0,1,1,0,0,-1,-1,0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Fry</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str"/>
+      <c r="B16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" t="str">
+        <v>搅拌机</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mixer</t>
+        </is>
+      </c>
+      <c r="E16" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="F16" t="str">
+        <v>0,1,1,0,0,-1,-1,0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Mixing</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str"/>
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" t="str">
+        <v>磨豆机</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Grinder</t>
+        </is>
+      </c>
+      <c r="E17" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="F17" t="str">
+        <v>0,1,1,0,0,-1,-1,0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Grind</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str"/>
+      <c r="B18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" t="str">
+        <v>咖啡机</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CoffeeMachine</t>
+        </is>
+      </c>
+      <c r="E18" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="F18" t="str">
+        <v>0,1,1,0,0,-1,-1,0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Extract</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str"/>
+      <c r="B19" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" t="str">
+        <v>蒸汽机</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SteamMachine</t>
+        </is>
+      </c>
+      <c r="E19" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="F19" t="str">
+        <v>0,1,1,0,0,-1,-1,0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>HeatMilk|FoamMilk</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>